--- a/elite-data/manifest-templates/EL_template_AssayMetabolomicsTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_AssayMetabolomicsTemplate.xlsx
@@ -403,7 +403,7 @@
     <t>AssayMetabolomicsTemplate</t>
   </si>
   <si>
-    <t>Not applicable</t>
+    <t>not applicable</t>
   </si>
   <si>
     <t>No</t>
@@ -439,7 +439,7 @@
     <t>Baker pool</t>
   </si>
   <si>
-    <t>Not collected</t>
+    <t>not collected</t>
   </si>
   <si>
     <t>AU/ml</t>
@@ -469,7 +469,7 @@
     <t>GoldenWest</t>
   </si>
   <si>
-    <t>Unknown</t>
+    <t>unknown</t>
   </si>
   <si>
     <t>g/l</t>
